--- a/exports/trend_1d/INDUSTOWER_full_report.xlsx
+++ b/exports/trend_1d/INDUSTOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.78</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42229</v>
+        <v>42230</v>
       </c>
       <c r="H2" t="n">
-        <v>416.55</v>
+        <v>395.25</v>
       </c>
       <c r="I2" t="n">
         <v>405.222874481133</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K2" t="n">
-        <v>27.09</v>
+        <v>20.59</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H3" t="n">
-        <v>395.25</v>
+        <v>411.1</v>
       </c>
       <c r="I3" t="n">
         <v>409.9545979179084</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-4.01</v>
       </c>
       <c r="L3" t="n">
         <v>6.31</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>18.46</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H4" t="n">
-        <v>380.9</v>
+        <v>374.15</v>
       </c>
       <c r="I4" t="n">
         <v>378.7367018048716</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.35</v>
+        <v>-8.99</v>
       </c>
       <c r="L4" t="n">
         <v>13.97</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="H5" t="n">
-        <v>337.5</v>
+        <v>342.4</v>
       </c>
       <c r="I5" t="n">
         <v>341.6959950650062</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="L5" t="n">
         <v>5.61</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42594</v>
+        <v>42598</v>
       </c>
       <c r="H6" t="n">
-        <v>352.8</v>
+        <v>337.35</v>
       </c>
       <c r="I6" t="n">
         <v>349.6248043260636</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K6" t="n">
-        <v>3.04</v>
+        <v>-1.47</v>
       </c>
       <c r="L6" t="n">
         <v>4.23</v>
@@ -783,7 +854,7 @@
         <v>0.67</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>4.38</v>
       </c>
       <c r="O6" t="n">
         <v>1.45</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.94</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42647</v>
+        <v>42648</v>
       </c>
       <c r="H7" t="n">
-        <v>355.8</v>
+        <v>362.6</v>
       </c>
       <c r="I7" t="n">
         <v>361.5222276388299</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.47</v>
+        <v>-7.48</v>
       </c>
       <c r="L7" t="n">
         <v>10.79</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42720</v>
+        <v>42723</v>
       </c>
       <c r="H8" t="n">
-        <v>342.75</v>
+        <v>332.45</v>
       </c>
       <c r="I8" t="n">
         <v>333.0161434353955</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.47</v>
+        <v>-8.31</v>
       </c>
       <c r="L8" t="n">
         <v>13.62</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.85</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42822</v>
+        <v>42823</v>
       </c>
       <c r="H9" t="n">
-        <v>307.1</v>
+        <v>324.65</v>
       </c>
       <c r="I9" t="n">
         <v>308.7866810471322</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>7.63</v>
+        <v>2.35</v>
       </c>
       <c r="L9" t="n">
         <v>4.66</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.07</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H10" t="n">
-        <v>383.4</v>
+        <v>369.7</v>
       </c>
       <c r="I10" t="n">
         <v>372.7922677728407</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K10" t="n">
-        <v>18.1</v>
+        <v>13.88</v>
       </c>
       <c r="L10" t="n">
         <v>5.38</v>
@@ -1011,7 +1130,7 @@
         <v>2.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="O10" t="n">
         <v>5.71</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42996</v>
+        <v>42997</v>
       </c>
       <c r="H11" t="n">
-        <v>375</v>
+        <v>383.85</v>
       </c>
       <c r="I11" t="n">
         <v>378.1279026422577</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.43</v>
+        <v>-3.83</v>
       </c>
       <c r="L11" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.34</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.41</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H12" t="n">
-        <v>438.9</v>
+        <v>403.35</v>
       </c>
       <c r="I12" t="n">
         <v>411.8525110176797</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12" t="n">
-        <v>14.34</v>
+        <v>5.08</v>
       </c>
       <c r="L12" t="n">
         <v>6.14</v>
@@ -1125,7 +1268,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.82</v>
+        <v>8.1</v>
       </c>
       <c r="O12" t="n">
         <v>2.36</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>18.57</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43285</v>
+        <v>43286</v>
       </c>
       <c r="H13" t="n">
-        <v>288.65</v>
+        <v>292.45</v>
       </c>
       <c r="I13" t="n">
         <v>290.7948691993392</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>28.44</v>
+        <v>27.49</v>
       </c>
       <c r="L13" t="n">
         <v>8.48</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.97</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43326</v>
+        <v>43328</v>
       </c>
       <c r="H14" t="n">
-        <v>273.6</v>
+        <v>270.45</v>
       </c>
       <c r="I14" t="n">
         <v>273.3263899498544</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.45</v>
+        <v>-7.52</v>
       </c>
       <c r="L14" t="n">
         <v>8.380000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.55</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43467</v>
+        <v>43468</v>
       </c>
       <c r="H15" t="n">
-        <v>254.65</v>
+        <v>261.75</v>
       </c>
       <c r="I15" t="n">
         <v>261.5484560943044</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K15" t="n">
-        <v>5.84</v>
+        <v>3.22</v>
       </c>
       <c r="L15" t="n">
         <v>5.05</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>10.3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H16" t="n">
-        <v>266.95</v>
+        <v>253.45</v>
       </c>
       <c r="I16" t="n">
         <v>257.4215025733395</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>1.99</v>
+        <v>-3.17</v>
       </c>
       <c r="L16" t="n">
-        <v>2.94</v>
+        <v>3.82</v>
       </c>
       <c r="M16" t="n">
         <v>0.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>5.06</v>
       </c>
       <c r="O16" t="n">
         <v>2.79</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>14.46</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43502</v>
+        <v>43503</v>
       </c>
       <c r="H17" t="n">
-        <v>285.6</v>
+        <v>294.75</v>
       </c>
       <c r="I17" t="n">
         <v>290.1045947093789</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-12.68</v>
+        <v>-16.3</v>
       </c>
       <c r="L17" t="n">
-        <v>13.93</v>
+        <v>17.3</v>
       </c>
       <c r="M17" t="n">
         <v>1.8</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H18" t="n">
-        <v>288.75</v>
+        <v>283.35</v>
       </c>
       <c r="I18" t="n">
         <v>284.1083890272994</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.04</v>
+        <v>-3.87</v>
       </c>
       <c r="L18" t="n">
         <v>4.97</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43775</v>
+        <v>43776</v>
       </c>
       <c r="H19" t="n">
-        <v>213.15</v>
+        <v>221.15</v>
       </c>
       <c r="I19" t="n">
         <v>217.4263291335077</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K19" t="n">
-        <v>24.78</v>
+        <v>21.95</v>
       </c>
       <c r="L19" t="n">
         <v>3.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>17.71</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H20" t="n">
-        <v>234.25</v>
+        <v>210.35</v>
       </c>
       <c r="I20" t="n">
         <v>218.246713076745</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K20" t="n">
-        <v>5.92</v>
+        <v>-4.88</v>
       </c>
       <c r="L20" t="n">
         <v>13.38</v>
       </c>
       <c r="M20" t="n">
-        <v>6.06</v>
+        <v>10.01</v>
       </c>
       <c r="N20" t="n">
-        <v>7.01</v>
+        <v>10.2</v>
       </c>
       <c r="O20" t="n">
         <v>3.75</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.78</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43963</v>
+        <v>43964</v>
       </c>
       <c r="H21" t="n">
-        <v>182.7</v>
+        <v>189.05</v>
       </c>
       <c r="I21" t="n">
         <v>185.4206353854669</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K21" t="n">
-        <v>13.14</v>
+        <v>10.13</v>
       </c>
       <c r="L21" t="n">
         <v>16.28</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>19.59</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44027</v>
+        <v>44028</v>
       </c>
       <c r="H22" t="n">
-        <v>196.55</v>
+        <v>183.1</v>
       </c>
       <c r="I22" t="n">
         <v>188.3241903342625</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K22" t="n">
-        <v>3.97</v>
+        <v>-3.15</v>
       </c>
       <c r="L22" t="n">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="M22" t="n">
         <v>4.74</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>19.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44076</v>
+        <v>44077</v>
       </c>
       <c r="H23" t="n">
-        <v>188.95</v>
+        <v>210.6</v>
       </c>
       <c r="I23" t="n">
         <v>204.9424284500778</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.19</v>
+        <v>-15.02</v>
       </c>
       <c r="L23" t="n">
-        <v>12.51</v>
+        <v>16.52</v>
       </c>
       <c r="M23" t="n">
         <v>3.61</v>
       </c>
       <c r="N23" t="n">
-        <v>4.26</v>
+        <v>11.46</v>
       </c>
       <c r="O23" t="n">
         <v>-6.84</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>20.09</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H24" t="n">
-        <v>181.9</v>
+        <v>173.85</v>
       </c>
       <c r="I24" t="n">
         <v>178.8226022495511</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.63</v>
+        <v>-17.45</v>
       </c>
       <c r="L24" t="n">
-        <v>14.55</v>
+        <v>17.92</v>
       </c>
       <c r="M24" t="n">
         <v>2.07</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>20.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44154</v>
+        <v>44155</v>
       </c>
       <c r="H25" t="n">
-        <v>179.15</v>
+        <v>211.1</v>
       </c>
       <c r="I25" t="n">
         <v>189.9264174250284</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.05</v>
+        <v>-21.43</v>
       </c>
       <c r="L25" t="n">
-        <v>14.06</v>
+        <v>23.64</v>
       </c>
       <c r="M25" t="n">
         <v>3.84</v>
       </c>
       <c r="N25" t="n">
-        <v>8.1</v>
+        <v>17.83</v>
       </c>
       <c r="O25" t="n">
         <v>-4.43</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>18.76</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H26" t="n">
-        <v>232.55</v>
+        <v>223.1</v>
       </c>
       <c r="I26" t="n">
         <v>228.092204211938</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K26" t="n">
-        <v>10.16</v>
+        <v>5.68</v>
       </c>
       <c r="L26" t="n">
         <v>14.07</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>18.33</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44250</v>
+        <v>44251</v>
       </c>
       <c r="H27" t="n">
-        <v>261.8</v>
+        <v>267.4</v>
       </c>
       <c r="I27" t="n">
         <v>262.198585762247</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-17.35</v>
+        <v>-19.86</v>
       </c>
       <c r="L27" t="n">
-        <v>19.99</v>
+        <v>21.81</v>
       </c>
       <c r="M27" t="n">
         <v>1.58</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>20.14</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44376</v>
+        <v>44377</v>
       </c>
       <c r="H28" t="n">
-        <v>232.95</v>
+        <v>230</v>
       </c>
       <c r="I28" t="n">
         <v>230.3722663155317</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K28" t="n">
-        <v>-12.88</v>
+        <v>-13.99</v>
       </c>
       <c r="L28" t="n">
         <v>15.28</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44445</v>
+        <v>44446</v>
       </c>
       <c r="H29" t="n">
-        <v>215.75</v>
+        <v>232.9</v>
       </c>
       <c r="I29" t="n">
         <v>227.1307612750685</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" t="n">
-        <v>6.2</v>
+        <v>-1.26</v>
       </c>
       <c r="L29" t="n">
         <v>2.37</v>
@@ -2094,7 +2441,7 @@
         <v>1.31</v>
       </c>
       <c r="N29" t="n">
-        <v>4.49</v>
+        <v>7.95</v>
       </c>
       <c r="O29" t="n">
         <v>-1.27</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.43</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H30" t="n">
-        <v>265</v>
+        <v>262.65</v>
       </c>
       <c r="I30" t="n">
         <v>264.4386849420346</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K30" t="n">
-        <v>13.78</v>
+        <v>12.77</v>
       </c>
       <c r="L30" t="n">
         <v>7.81</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.55</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44571</v>
+        <v>44572</v>
       </c>
       <c r="H31" t="n">
-        <v>251.75</v>
+        <v>257.85</v>
       </c>
       <c r="I31" t="n">
         <v>257.2784287695011</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>4.15</v>
+        <v>1.83</v>
       </c>
       <c r="L31" t="n">
         <v>12.64</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H32" t="n">
-        <v>249.3</v>
+        <v>239.55</v>
       </c>
       <c r="I32" t="n">
         <v>242.2367489677139</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.32</v>
+        <v>-7.1</v>
       </c>
       <c r="L32" t="n">
-        <v>5.16</v>
+        <v>7.89</v>
       </c>
       <c r="M32" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>3.91</v>
       </c>
       <c r="O32" t="n">
         <v>2.42</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H33" t="n">
-        <v>203.6</v>
+        <v>208.25</v>
       </c>
       <c r="I33" t="n">
         <v>203.7407371382108</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K33" t="n">
-        <v>15.01</v>
+        <v>13.07</v>
       </c>
       <c r="L33" t="n">
         <v>8.220000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>9.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44775</v>
+        <v>44776</v>
       </c>
       <c r="H34" t="n">
-        <v>211.4</v>
+        <v>198.95</v>
       </c>
       <c r="I34" t="n">
         <v>202.6123606051219</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>1.51</v>
+        <v>-4.47</v>
       </c>
       <c r="L34" t="n">
-        <v>6.65</v>
+        <v>6.89</v>
       </c>
       <c r="M34" t="n">
-        <v>1.38</v>
+        <v>3.36</v>
       </c>
       <c r="N34" t="n">
-        <v>3.67</v>
+        <v>5.89</v>
       </c>
       <c r="O34" t="n">
         <v>2.28</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>11.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H35" t="n">
-        <v>190.05</v>
+        <v>194.1</v>
       </c>
       <c r="I35" t="n">
         <v>193.9597114605106</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K35" t="n">
-        <v>4.47</v>
+        <v>2.44</v>
       </c>
       <c r="L35" t="n">
         <v>3.64</v>
       </c>
       <c r="M35" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="N35" t="n">
         <v>6.22</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.23</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H36" t="n">
-        <v>184.95</v>
+        <v>183.75</v>
       </c>
       <c r="I36" t="n">
         <v>184.667298284754</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.71</v>
+        <v>-5.33</v>
       </c>
       <c r="L36" t="n">
         <v>8.630000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44966</v>
+        <v>44967</v>
       </c>
       <c r="H37" t="n">
-        <v>153.6</v>
+        <v>161.9</v>
       </c>
       <c r="I37" t="n">
         <v>161.5172424080517</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K37" t="n">
-        <v>16.41</v>
+        <v>11.89</v>
       </c>
       <c r="L37" t="n">
         <v>2.29</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>18.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H38" t="n">
-        <v>146.4</v>
+        <v>144</v>
       </c>
       <c r="I38" t="n">
         <v>144.5302813099918</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.57</v>
+        <v>-11.06</v>
       </c>
       <c r="L38" t="n">
-        <v>10.35</v>
+        <v>11.98</v>
       </c>
       <c r="M38" t="n">
         <v>1.58</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.23</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H39" t="n">
-        <v>139.6</v>
+        <v>149.4</v>
       </c>
       <c r="I39" t="n">
         <v>142.0237360218881</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" t="n">
-        <v>3.06</v>
+        <v>-3.75</v>
       </c>
       <c r="L39" t="n">
-        <v>3.54</v>
+        <v>7.36</v>
       </c>
       <c r="M39" t="n">
         <v>1.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.61</v>
+        <v>7.02</v>
       </c>
       <c r="O39" t="n">
         <v>-1.64</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.45</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H40" t="n">
-        <v>164.2</v>
+        <v>154.7</v>
       </c>
       <c r="I40" t="n">
         <v>155.3813332391699</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K40" t="n">
-        <v>9.91</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>8.67</v>
@@ -2721,7 +3200,7 @@
         <v>2.22</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>5.79</v>
       </c>
       <c r="O40" t="n">
         <v>7.02</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.68</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45166</v>
+        <v>45167</v>
       </c>
       <c r="H41" t="n">
-        <v>166.35</v>
+        <v>168.6</v>
       </c>
       <c r="I41" t="n">
         <v>166.7955439893489</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.53</v>
+        <v>-8.99</v>
       </c>
       <c r="L41" t="n">
-        <v>9.02</v>
+        <v>10.76</v>
       </c>
       <c r="M41" t="n">
         <v>1.44</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H42" t="n">
-        <v>171.35</v>
+        <v>167.95</v>
       </c>
       <c r="I42" t="n">
         <v>168.4096734199929</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K42" t="n">
-        <v>1.63</v>
+        <v>-0.39</v>
       </c>
       <c r="L42" t="n">
-        <v>0.98</v>
+        <v>1.87</v>
       </c>
       <c r="M42" t="n">
         <v>0.64</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45247</v>
+        <v>45250</v>
       </c>
       <c r="H43" t="n">
-        <v>179.85</v>
+        <v>185.25</v>
       </c>
       <c r="I43" t="n">
         <v>183.8612143071015</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.09</v>
+        <v>-10.3</v>
       </c>
       <c r="L43" t="n">
         <v>10.75</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.91</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H44" t="n">
-        <v>189.55</v>
+        <v>174.1</v>
       </c>
       <c r="I44" t="n">
         <v>174.7159151399646</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>2.32</v>
+        <v>-6.02</v>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>7.88</v>
       </c>
       <c r="M44" t="n">
         <v>0.31</v>
       </c>
       <c r="N44" t="n">
-        <v>2.54</v>
+        <v>8.15</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>16.11</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45293</v>
+        <v>45294</v>
       </c>
       <c r="H45" t="n">
-        <v>194.8</v>
+        <v>200.15</v>
       </c>
       <c r="I45" t="n">
         <v>197.4767830766692</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-11.89</v>
+        <v>-14.96</v>
       </c>
       <c r="L45" t="n">
-        <v>15.68</v>
+        <v>15.88</v>
       </c>
       <c r="M45" t="n">
         <v>1.04</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.72</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H46" t="n">
-        <v>350.8</v>
+        <v>296.8</v>
       </c>
       <c r="I46" t="n">
         <v>309.6322990078735</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K46" t="n">
-        <v>75.27</v>
+        <v>48.29</v>
       </c>
       <c r="L46" t="n">
         <v>3.55</v>
@@ -3063,7 +3614,7 @@
         <v>3.13</v>
       </c>
       <c r="N46" t="n">
-        <v>5.57</v>
+        <v>15.39</v>
       </c>
       <c r="O46" t="n">
         <v>2.75</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>23.45</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="H47" t="n">
-        <v>351.9</v>
+        <v>361.7</v>
       </c>
       <c r="I47" t="n">
         <v>361.6191054977251</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.56</v>
+        <v>-21.87</v>
       </c>
       <c r="L47" t="n">
-        <v>19.88</v>
+        <v>24.95</v>
       </c>
       <c r="M47" t="n">
         <v>3.67</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.13</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H48" t="n">
-        <v>412.7</v>
+        <v>375.65</v>
       </c>
       <c r="I48" t="n">
         <v>403.311599997358</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" t="n">
-        <v>14.1</v>
+        <v>3.86</v>
       </c>
       <c r="L48" t="n">
-        <v>1.41</v>
+        <v>2.39</v>
       </c>
       <c r="M48" t="n">
         <v>2.03</v>
       </c>
       <c r="N48" t="n">
-        <v>4.52</v>
+        <v>8.98</v>
       </c>
       <c r="O48" t="n">
         <v>2.78</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>15.07</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H49" t="n">
-        <v>334.1</v>
+        <v>341.05</v>
       </c>
       <c r="I49" t="n">
         <v>337.3979510271805</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K49" t="n">
-        <v>11.06</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L49" t="n">
         <v>10.54</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>9.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H50" t="n">
-        <v>322.85</v>
+        <v>321.45</v>
       </c>
       <c r="I50" t="n">
         <v>322.5711969627785</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.34</v>
+        <v>-5.75</v>
       </c>
       <c r="L50" t="n">
-        <v>6.01</v>
+        <v>7.55</v>
       </c>
       <c r="M50" t="n">
         <v>1.69</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.31</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H51" t="n">
-        <v>341.7</v>
+        <v>349.55</v>
       </c>
       <c r="I51" t="n">
         <v>342.561090138897</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.3</v>
+        <v>-8.74</v>
       </c>
       <c r="L51" t="n">
-        <v>8.83</v>
+        <v>9.43</v>
       </c>
       <c r="M51" t="n">
         <v>3.19</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>10.82</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H52" t="n">
-        <v>336.1</v>
+        <v>323.35</v>
       </c>
       <c r="I52" t="n">
         <v>325.9473970954945</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.85</v>
+        <v>-7.5</v>
       </c>
       <c r="L52" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M52" t="n">
         <v>1.62</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>14.34</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H53" t="n">
-        <v>339.65</v>
+        <v>348.2</v>
       </c>
       <c r="I53" t="n">
         <v>346.1949897145115</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.04</v>
+        <v>-7.69</v>
       </c>
       <c r="L53" t="n">
-        <v>7.56</v>
+        <v>8.1</v>
       </c>
       <c r="M53" t="n">
         <v>4.66</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.74</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H54" t="n">
-        <v>389.5</v>
+        <v>381.95</v>
       </c>
       <c r="I54" t="n">
         <v>384.6471173053163</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K54" t="n">
-        <v>11.86</v>
+        <v>9.69</v>
       </c>
       <c r="L54" t="n">
         <v>6.96</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H55" t="n">
-        <v>336.65</v>
+        <v>340.45</v>
       </c>
       <c r="I55" t="n">
         <v>338.1694629178102</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K55" t="n">
-        <v>11.86</v>
+        <v>10.87</v>
       </c>
       <c r="L55" t="n">
         <v>2.83</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.84</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H56" t="n">
-        <v>426</v>
+        <v>408.55</v>
       </c>
       <c r="I56" t="n">
         <v>421.7489887179365</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K56" t="n">
-        <v>25.13</v>
+        <v>20</v>
       </c>
       <c r="L56" t="n">
         <v>4.38</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>11.51</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H57" t="n">
-        <v>416.4</v>
+        <v>422.95</v>
       </c>
       <c r="I57" t="n">
         <v>422.6887190630035</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.92</v>
+        <v>-3.52</v>
       </c>
       <c r="L57" t="n">
         <v>4.68</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.51</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="H58" t="n">
-        <v>398.4</v>
+        <v>385.5</v>
       </c>
       <c r="I58" t="n">
         <v>390.7184954798056</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.8</v>
+        <v>-8.85</v>
       </c>
       <c r="L58" t="n">
-        <v>6.9</v>
+        <v>9.09</v>
       </c>
       <c r="M58" t="n">
         <v>0.62</v>
       </c>
       <c r="N58" t="n">
-        <v>2.39</v>
+        <v>3.24</v>
       </c>
       <c r="O58" t="n">
         <v>1.57</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8765,7 +9480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="6">
@@ -8775,7 +9490,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -8785,7 +9500,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -8795,7 +9510,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -8805,7 +9520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -8815,7 +9530,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150.8</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="11">
@@ -8855,7 +9570,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.86</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -8865,7 +9580,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -8875,7 +9590,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.16</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="17">
@@ -8885,7 +9600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75.27</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="18">
@@ -8895,7 +9610,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19">
@@ -8905,7 +9620,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.06</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="20">
@@ -8915,7 +9630,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.96</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="21">
@@ -8925,7 +9640,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.99</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="22">
@@ -8935,7 +9650,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -8945,7 +9660,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -8955,7 +9670,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="25">
@@ -8965,7 +9680,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.87</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="26">
@@ -8975,7 +9690,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.54</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="27">
@@ -8995,7 +9710,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
